--- a/tests/integration_workspace/dashboard_full_pipeline/output/DASHBOARD.xlsx
+++ b/tests/integration_workspace/dashboard_full_pipeline/output/DASHBOARD.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18:55:01</t>
+          <t>16:36:59</t>
         </is>
       </c>
     </row>

--- a/tests/integration_workspace/dashboard_full_pipeline/output/DASHBOARD.xlsx
+++ b/tests/integration_workspace/dashboard_full_pipeline/output/DASHBOARD.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:36:59</t>
+          <t>09:07:43</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15 sec</t>
+          <t>13 sec</t>
         </is>
       </c>
     </row>
